--- a/data_extactor/batch_10_fa/batch_0099_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0099_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دقت کنترل | درک شفاهی | حساسیت به مشکل | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | هماهنگی چند عضو | سرعت ادراکی | توجه انتخابی | بینایی نزدیک | وضوح گفتار | بینایی دور | قدرت ایستا | چالاکی دست | ثبات بازو-دست | انعطاف‌پذیری بستار | بیان کتبی | تجسم | ترتیب‌دهی اطلاعات | درک عمق | قدرت تنه | کنترل سرعت | چالاکی انگشتان | حساسیت شنوایی</t>
+          <t>دقت کنترل | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | هماهنگی چند عضو | سرعت ادراکی | توجه انتخابی | بینایی نزدیک | وضوح گفتار | بینایی دور | قدرت ایستا | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | تجسم | ترتیب‌دهی اطلاعات | درک عمق | قدرت تنه | کنترل نرخ | مهارت انگشتان | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دمای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان به صورت ایستاده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سرعت تعیین‌شده توسط سرعت تجهیزات | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای ایستادن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | اپراتورهای تجهیزات کشاورزی | اپراتورهای جرثقیل و تاور | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، پاتیل، خشک‌کن و دیگ | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌آلات بارگیری و جابجایی، معدن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | بارگیران واگن مخزنی، کامیون و کشتی</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | اپراتورهای تجهیزات کشاورزی | اپراتورهای جرثقیل و تاور | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکسترود و کشش، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | بارگیران واگن مخزنی، کامیون و کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال | درک مطلب | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | درک عمق | کنترل سرعت | زمان عکس‌العمل | ثبات بازو-دست | حساسیت به مشکل | جهت‌گیری پاسخ | چالاکی دست | توجه انتخابی | بینایی نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | تجسم | سرعت ادراکی | درک شفاهی | حساسیت به درخشندگی شدید | چالاکی انگشتان | اشتراک زمانی | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | درک عمق | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | حساسیت به مسئله | جهت‌گیری پاسخ | مهارت دستی | توجه انتخابی | بینایی نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | تجسم | سرعت ادراکی | درک شفاهی | حساسیت به درخشندگی شدید | مهارت انگشتان | تقسیم توجه | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | محیط سرپوشیده، بدون کنترل شرایط محیطی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دمای بسیار گرم یا سرد | فشار زمانی | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | سرعت تعیین‌شده توسط سرعت تجهیزات | داخل وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض ارتفاعات بالا | پیامدهای کاری و نتایج سایر کارگران | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پیامد خطا | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | فضای باز، در معرض تمام شرایط آب و هوایی | سرعت تعیین‌شده توسط سرعت تجهیزات | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض ارتفاعات بالا | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای ماشین‌آلات حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌آلات بارگیری و جابجایی، معدن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | میل‌رایت‌ها | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | ریگرها | کارگران آهن و فولاد سازه‌ای | بارگیران واگن مخزنی، کامیون و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | ریگرها | کارگران سازه‌های آهنی و فولادی | بارگیران واگن مخزنی، کامیون و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | درک عمق | زمان عکس‌العمل | چالاکی دست | ثبات بازو-دست | بینایی نزدیک | بینایی دور | حساسیت به مشکل | حساسیت شنوایی | چالاکی انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | توجه شنوایی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | درک عمق | زمان عکس‌العمل | مهارت دستی | ثبات دست و بازو | بینایی نزدیک | بینایی دور | حساسیت به مسئله | حساسیت شنوایی | مهارت انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء, ابزارها یا کنترل‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دمای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر سقف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | صرف زمان به صورت نشسته</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | ارتباط با دیگران | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فضای باز، زیر سقف | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای دکل، نفت و گاز | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | کمک‌کاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده، نفت و گاز | ملوانان و روغن‌کاران دریایی | اپراتورهای واحد خدمات، نفت و گاز | پمپ‌چی‌های سرچاهی</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای دکل، نفت و گاز | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--کارگران استخراج | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | ملوانان و روغن‌کاران دریایی | اپراتورهای واحد خدمات، نفت و گاز | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | مانیتورینگ | گوش دادن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | زمان عکس‌العمل | درک عمق | ثبات بازو-دست | دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | استدلال قیاسی | بیان شفاهی | درک شفاهی | چالاکی دست | توجه انتخابی | تشخیص گفتار | کنترل سرعت | بینایی دور | حساسیت شنوایی | وضوح گفتار | تجسم | استدلال استقرایی | سرعت ادراکی | ترتیب‌دهی اطلاعات | تعادل کلی بدن | انعطاف‌پذیری گسترده | چالاکی انگشتان | انعطاف‌پذیری دسته‌بندی | توجه شنوایی | جهت‌گیری پاسخ</t>
+          <t>حساسیت به مسئله | زمان عکس‌العمل | درک عمق | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | استدلال قیاسی | بیان شفاهی | درک شفاهی | مهارت دستی | توجه انتخابی | تشخیص گفتار | کنترل نرخ | بینایی دور | حساسیت شنوایی | وضوح گفتار | تجسم | استدلال استقرایی | سرعت ادراکی | ترتیب‌دهی اطلاعات | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض ارتفاعات بالا | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | پیامد خطا | صرف زمان برای خم شدن یا چرخاندن بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | داخل وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض دمای بسیار گرم یا سرد | محیط سرپوشیده، بدون کنترل شرایط محیطی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فشار زمانی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | قرار گرفتن در معرض تجهیزات خطرناک | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض ارتفاعات بالا | فراوانی تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | پیامد خطا | صرف زمان برای خم کردن یا چرخاندن بدن | سرعت تعیین‌شده توسط سرعت تجهیزات | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض شرایط خطرناک | ارتباط با دیگران | قرار گرفتن در معرض ارتعاش کل بدن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | نصب‌کنندگان و تعمیرکنندگان خطوط انتقال نیروی برق | اپراتورهای ماشین‌آلات حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار, کالا و مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌تراش و تراشکاری فلز و پلاستیک | اپراتورهای ماشین‌آلات بارگیری و جابجایی، معدن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات چندکاره فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای شمع‌کوب | ریگرها | کارگران ساده، نفت و گاز | بارگیران واگن مخزنی، کامیون و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | اپراتورهای لایروب | نصابان و تعمیرکاران خطوط انتقال نیروی برق | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | اپراتورهای کوبنده شمع | ریگرها | کارگران فنی همه‌کاره نفت و گاز | بارگیران واگن مخزنی، کامیون و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | جهت‌گیری پاسخ | چالاکی دست | کنترل سرعت | زمان عکس‌العمل | درک عمق | حساسیت به مشکل | توجه شنوایی | بینایی نزدیک | قدرت تنه | قدرت ایستا | ثبات بازو-دست | توجه انتخابی | تجسم | جهت‌گیری فضایی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | چالاکی انگشتان | بیان شفاهی | درک شفاهی | بینایی محیطی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | جهت‌گیری پاسخ | مهارت دستی | کنترل نرخ | زمان عکس‌العمل | درک عمق | حساسیت به مسئله | توجه شنیداری | بینایی نزدیک | قدرت تنه | قدرت ایستا | ثبات دست و بازو | توجه انتخابی | تجسم | جهت‌گیری فضایی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | بیان شفاهی | درک شفاهی | بینایی محیطی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض دمای بسیار گرم یا سرد | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | در وسیله نقلیه روباز یا کار با تجهیزات | پیامد خطا | فراوانی تصمیم‌گیری | محیط سرپوشیده، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارگران | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای خم شدن یا چرخاندن بدن | سطح رقابت | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | فشار زمانی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | در یک وسیله نقلیه روباز یا کار با تجهیزات | پیامد خطا | فراوانی تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای انجام حرکات تکراری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سرعت تعیین‌شده توسط سرعت تجهیزات | صرف زمان برای خم کردن یا چرخاندن بدن | سطح رقابت | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای تجهیزات کشاورزی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین‌آلات استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | مونتاژکنندگان موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌آلات حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | رانندگان کامیون‌های سنگین و تریلی | کمک‌کاران--کارگران تولید | اپراتورهای بالابر و وینچ | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌آلات بارگیری و جابجایی، معدن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتور | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مکانیک‌های تجهیزات فضای باز و سایر موتورهای کوچک | اپراتورهای تجهیزات روسازی، آسفالت و کوبش | اپراتورهای شمع‌کوب | ریگرها | بارگیران واگن مخزنی، کامیون و کشتی</t>
+          <t>اپراتورهای تجهیزات کشاورزی | مکانیک‌های اتوبوس و کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین استخراج مداوم | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | رانندگان کامیون‌های سنگین و تریلی | کمک‌کاران--کارگران تولید | اپراتورهای بالابر و وینچ | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | اپراتورهای ماشین‌های بارگیری و انتقال، معدن‌کاری زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | مکانیک‌های تجهیزات برق فضای باز و سایر موتورهای کوچک | اپراتورهای تجهیزات روسازی، زیرسازی و کوبش | اپراتورهای کوبنده شمع | ریگرها | بارگیران واگن مخزنی، کامیون و کشتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | زبان انگلیسی | ترابری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | چالاکی دست | انعطاف‌پذیری گسترده | هماهنگی چند عضو | حساسیت به مشکل | استقامت | قدرت تنه | دقت کنترل | چالاکی انگشتان</t>
+          <t>بینایی نزدیک | مهارت دستی | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | حساسیت به مسئله | استقامت | قدرت تنه | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>داخل وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط سرپوشیده، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | فشار زمانی | صرف زمان به صورت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای راه رفتن یا دویدن | فضای باز، زیر سقف | قرار گرفتن در معرض دمای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | صرف زمان برای خم شدن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | ارتباط با دیگران</t>
+          <t>در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای انجام حرکات تکراری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، بدون کنترل شرایط محیطی | آزادی در تصمیم‌گیری | فشار زمانی | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای راه رفتن یا دویدن | فضای باز، زیر سقف | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | صرف زمان برای خم کردن یا چرخاندن بدن | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های پوشش‌دهی، رنگ‌آمیزی و پاشش | نصب‌کنندگان و تعمیرکنندگان کنترل و شیرآلات، به جز درب‌های مکانیکی | ظرفشوی‌ها | تعمیرکنندگان موتورهای الکتریکی، ابزارهای برقی و موارد مرتبط | اپراتورها و متصدیان کوره، پاتیل، خشک‌کن و دیگ | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تعمیرکنندگان لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران خشکشویی و لباسشویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای پمپ، به جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله فاضلاب | تیزکنندگان و سنگ‌زن‌های ابزار</t>
+          <t>اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، نقاشی و اسپری | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | ظرف‌شوی‌ها | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | سرایداران و تمیزکنندگان، به جز خدمتکاران و تمیزکنندگان خانه‌داری | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره تصفیه فلز | اپراتورهای پمپ، به جز پمپ‌کنندگان سرچاهی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Apple Safari | Autodesk AutoCAD | نرم‌افزار ورود داده | FaceTime | Google Docs | نرم‌افزار دستگاه کامپیوتر دستی | IBM Notes | سیستم‌های مدیریت موجودی | نرم‌افزار ردیابی موجودی | نرم‌افزار کنترل ماشین | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Publisher | Microsoft Word | Mozilla Firefox | Oracle Database | نرم‌افزار SAP | سیستم مدیریت انبار WMS</t>
+          <t>Apple Safari | Autodesk AutoCAD | نرم‌افزار ورود داده | FaceTime | Google Docs | نرم‌افزار دستگاه‌های کامپیوتر جیبی | IBM Notes | سیستم‌های مدیریت موجودی | نرم‌افزار ردیابی موجودی | نرم‌افزار کنترل ماشین | Microsoft Edge | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft Publisher | Microsoft Word | Mozilla Firefox | Oracle Database | نرم‌افزار SAP | سیستم مدیریت انبار WMS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و شخصی | ایمنی و امنیت عمومی | ترابری | تولید و فرآوری | ریاضیات</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | حمل و نقل | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>قدرت ایستا | قدرت تنه | هماهنگی چند عضو | بینایی نزدیک | انعطاف‌پذیری گسترده | استقامت | چالاکی دست | درک شفاهی | ثبات بازو-دست | توجه انتخابی | استدلال قیاسی | حساسیت به مشکل | بیان شفاهی | بینایی دور | قدرت پویا | دقت کنترل</t>
+          <t>قدرت ایستا | قدرت تنه | هماهنگی چند عضو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | مهارت دستی | درک شفاهی | ثبات دست و بازو | توجه انتخابی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | بینایی دور | قدرت پویا | دقت کنترل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دمای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف یکسان | صرف زمان به صورت ایستاده | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | در وسیله نقلیه روباز یا کار با تجهیزات | فراوانی تصمیم‌گیری | فضای باز، زیر سقف | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | فشار زمانی | پیامد خطا | تاثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط خطرناک | سلامت و ایمنی سایر کارگران | محیط سرپوشیده، بدون کنترل شرایط محیطی</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض آلاینده‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | اهمیت دقیق یا درست بودن | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت تکرار وظایف یکسان | صرف زمان برای ایستادن | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه روباز یا کار با تجهیزات | فراوانی تصمیم‌گیری | فضای باز، زیر سقف | آزادی در تصمیم‌گیری | ارتباط با دیگران | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | فشار زمانی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | قرار گرفتن در معرض شرایط خطرناک | سلامت و ایمنی سایر کارکنان | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردکن، آسیاب و پولیش | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | کمک‌کاران--کارگران استخراج | کمک‌کاران--کارگران تولید | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارگران خشکشویی و لباسشویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | کارگران بازیافت و احیا | کارمندان ارسال، دریافت و موجودی | بارگیران واگن مخزنی، کامیون و کشتی | وزن‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اطلاعات</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تمیزکنندگان وسایل نقلیه و تجهیزات | کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاور | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | دستیاران--کارگران استخراج | کمک‌کاران--کارگران تولید | اپراتورهای بالابر و وینچ | اپراتورهای تراکتور و کامیون صنعتی | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | کارگران بازیافت و احیا | کارمندان ارسال، دریافت و موجودی کالا | بارگیران واگن مخزنی، کامیون و کشتی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,32 +902,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار برنامه‌ریزی کاری</t>
+          <t>Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | مانیتورینگ</t>
+          <t>گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | مدیریت و امور اداری | ایمنی و امنیت عمومی | آموزش و پرورش | خدمات مشتریان و شخصی | زبان انگلیسی | پرسنل و منابع انسانی</t>
+          <t>تولید و فرآوری | مکانیک | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چالاکی دست | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | ثبات بازو-دست | انعطاف‌پذیری دسته‌بندی | چالاکی انگشتان | قدرت تنه | زمان عکس‌العمل | کنترل سرعت | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | بینایی دور | سرعت حرکت اعضا</t>
+          <t>مهارت دستی | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | بینایی دور | سرعت حرکت اعضا</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | صرف زمان به صورت ایستاده | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض دمای بسیار گرم یا سرد | فضای باز، زیر سقف | کار با یا مشارکت در یک گروه کاری یا تیم | در وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | صرف زمان برای خم شدن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن | پیامدهای کاری و نتایج سایر کارگران | آزادی در تصمیم‌گیری | فشار زمانی</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فضای باز، زیر سقف | کار با یا مشارکت در یک گروه کاری یا تیم | در یک وسیله نقلیه روباز یا کار با تجهیزات | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای خم کردن یا چرخاندن بدن | صرف زمان برای راه رفتن یا دویدن | پیامدهای کاری و نتایج سایر کارکنان | آزادی در تصمیم‌گیری | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورهای سیستم و پالایشگاه شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان نوار نقاله | کارگران حذف مواد خطرناک | کمک‌کاران--کارگران استخراج | کمک‌کاران--کارگران تولید | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران خشکشویی و لباسشویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی نگهداری و تعمیرات | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | هماهنگ‌کنندگان بازیافت | جمع‌آوران زباله و مواد بازیافتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | سرویس‌کاران سپتیک تانک و تمیزکنندگان لوله فاضلاب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
+          <t>اپراتورهای کارخانه و سامانه‌های شیمیایی | تمیزکنندگان وسایل نقلیه و تجهیزات | اپراتورها و متصدیان تجهیزات تمیزکاری، شستشو و اسیدشویی فلزات | اپراتورها و متصدیان نوار نقاله | کارگران حذف مواد خطرناک | دستیاران--کارگران استخراج | کمک‌کاران--کارگران تولید | مکانیک‌های ماشین‌آلات صنعتی | اپراتورهای تراکتور و کامیون صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران نگهداری و تعمیرات عمومی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | هماهنگ‌کنندگان بازیافت | جمع‌آوران زباله و مواد بازیافتی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ</t>
+          <t>نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات بازو-دست | دقت کنترل | کنترل سرعت | زمان عکس‌العمل | بینایی نزدیک | بیان شفاهی | حساسیت به مشکل | درک شفاهی | قدرت ایستا | چالاکی دست | ترتیب‌دهی اطلاعات</t>
+          <t>ثبات دست و بازو | دقت کنترل | کنترل نرخ | زمان عکس‌العمل | بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | درک شفاهی | قدرت ایستا | مهارت دستی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان به صورت ایستاده | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا آزاردهنده | سرعت تعیین‌شده توسط سرعت تجهیزات | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | صرف زمان برای انجام حرکات تکراری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | سرعت تعیین‌شده توسط سرعت تجهیزات | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | قرار گرفتن در معرض آلاینده‌ها | فشار زمانی | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردکن، آسیاب و پولیش | برش‌دهنده‌ها و هرس‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، پاتیل، خشک‌کن و دیگ | کارگران پرداخت و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های فرز و رنده فلز و پلاستیک | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | تیزکنندگان و سنگ‌زن‌های ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان کوره، کوره پخت، فر، خشک‌کن و دیگ بخار | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | بسته‌بندهای دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های نورد، فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین برش منسوجات | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ</t>
+          <t>نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و شخصی</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | قدرت تنه | حساسیت به مشکل | تشخیص گفتار | قدرت ایستا | هماهنگی چند عضو | چالاکی دست | درک شفاهی</t>
+          <t>بینایی نزدیک | قدرت تنه | حساسیت به مسئله | تشخیص گفتار | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | درک شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | استفاده از تجهیزات محافظتی یا ایمنی معمولی مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان به صورت ایستاده | محیط سرپوشیده، بدون کنترل شرایط محیطی | ارتباط با دیگران | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارگران</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | اهمیت دقیق یا درست بودن | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | ارتباط با دیگران | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای انجام حرکات تکراری | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض آلاینده‌ها | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های خردکن، آسیاب و پولیش | برش‌دهنده‌ها و هرس‌کنندگان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکسترود، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندی‌کنندگان و مرتب‌کنندگان محصولات کشاورزی | کارگران پرداخت و پولیش دستی | کمک‌کاران--کارگران تولید | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارگران خشکشویی و لباسشویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب‌کننده | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های کالاهای کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های جداسازی، فیلتراسیون، شفاف‌سازی، رسوب‌دهی و تقطیر | اپراتورهای چرخ خیاطی | وزن‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اطلاعات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برش‌دهندگان و پرداخت‌کاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | اپراتورها و متصدیان ماشین‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و تنباکو | درجه‌بندها و مرتب‌کنندگان محصولات کشاورزی | کارگران سنگ‌زنی و پرداخت دستی | کمک‌کاران--کارگران تولید | کارگران و جابجا‌کنندگان دستی بار، کالا و مواد | کارکنان خشک‌شویی و لباس‌شویی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های مخلوط‌کن و ترکیب‌کننده | قالب‌سازان، شکل‌دهندگان و ریخته‌گران، به جز فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کاران، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، زلال‌سازی، ته‌نشینی و تقطیر | اپراتورهای چرخ خیاطی | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0099_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0099_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دقت کنترل | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | هماهنگی چنداندامی | سرعت ادراک | توجه انتخابی | دید نزدیک | وضوح گفتار | دید دور | استحکام ایستا | چابکی دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | تجسم فضایی | مرتب‌سازی اطلاعات | ادراک عمق | قدرت تنه | کنترل نرخ | چابکی انگشتان | حساسیت شنوایی</t>
+          <t>دقت کنترل | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | هماهنگی چند عضو | سرعت ادراکی | توجه انتخابی | بینایی نزدیک | وضوح گفتار | بینایی دور | قدرت ایستا | مهارت دستی | ثبات دست و بازو | انعطاف‌پذیری بستار | بیان کتبی | تجسم | ترتیب‌دهی اطلاعات | درک عمق | قدرت تنه | کنترل نرخ | مهارت انگشتان | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | اپراتورهای ماشین‌آلات کشاورزی | اپراتورهای جرثقیل و تاورکرین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های سنگ‌شکن، خردکن و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره، دیگ پخت، اتوکلاو و خشک‌کن صنعتی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات مهندسی و تجهیزات ساختمانی | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | اپراتورهای ماشین‌آلات و ادوات کشاورزی | اپراتورهای جرثقیل و تاورکرین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | درک مطلب | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چنداندامی | دید دور | ادراک عمق | کنترل نرخ | زمان واکنش | ثبات دست و بازو | حساسیت به مسئله | جهت‌یابی پاسخ | چابکی دستی | توجه انتخابی | دید نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | تمایز رنگ‌های بصری | تجسم فضایی | سرعت ادراک | درک شفاهی | حساسیت به خیرگی نور | چابکی انگشتان | تقسیم زمان | جهت‌یابی فضایی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | درک عمق | کنترل نرخ | زمان عکس‌العمل | ثبات دست و بازو | حساسیت به مسئله | جهت‌گیری پاسخ | مهارت دستی | توجه انتخابی | بینایی نزدیک | بیان شفاهی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | تجسم | سرعت ادراکی | درک شفاهی | حساسیت به درخشندگی شدید | مهارت انگشتان | تقسیم توجه | جهت‌گیری فضایی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، مهارها و سیستم‌های هواگرد | کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای درگ‌لاین و ماشین‌آلات حفاری و بارگیری در معادن روباز | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌کاران و نصابان ماشین‌آلات صنعتی (میلرایت) | مکانیک‌های ماشین‌آلات سنگین متحرک (به‌جز موتور) | اپراتورهای ماشین‌آلات مهندسی و تجهیزات ساختمانی | اپراتورهای دستگاه‌های شمع‌کوبی | ریگرها و سیم‌بکسل‌اندازان صنعتی | اسکلت‌کاران فلزی و تیرآهن‌کاران | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | اپراتورهای بالابر و وینچ | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | اسکلت‌سازان و نصابان سازه‌های فولادی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HYPACK DREDGEPACK | نرم‌افزار کنترل‌کننده منطقی قابل‌برنامه‌ریزی PLC | Teledyne Odom Hydrographic ODOM eChart | Trimble HYDROpro | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HYPACK DREDGEPACK | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | Teledyne Odom Hydrographic ODOM eChart | Trimble HYDROpro | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و امور اداری</t>
+          <t>مکانیک | زبان انگلیسی | ایمنی و امنیت عمومی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چنداندامی | ادراک عمق | زمان واکنش | چابکی دستی | ثبات دست و بازو | دید نزدیک | دید دور | حساسیت به مسئله | حساسیت شنوایی | چابکی انگشتان | توجه انتخابی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
+          <t>دقت کنترل | هماهنگی چند عضو | درک عمق | زمان عکس‌العمل | مهارت دستی | ثبات دست و بازو | بینایی نزدیک | بینایی دور | حساسیت به مسئله | حساسیت شنوایی | مهارت انگشتان | توجه انتخابی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | توجه شنیداری</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورهای ماشین‌آلات استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای دکل حفاری نفت و گاز | حفاران چاه‌های غیرنفت و گاز | اپراتورهای درگ‌لاین و ماشین‌آلات حفاری و بارگیری در معادن روباز | کارگران کمکی استخراج معدن و نفت | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات مهندسی و تجهیزات ساختمانی | اپراتورهای دستگاه‌های شمع‌کوبی | اپراتورهای پمپ (به‌جز پمپ‌های سرچاهی) | ریگرها و سیم‌بکسل‌اندازان صنعتی | حفاران دورانی نفت و گاز | کارگران همه‌کاره دکل‌های نفت و گاز (راستابات) | ملوانان و روغن‌کاران موتورخانه شناورها | اپراتورهای خدمات فنی چاه‌های نفت و گاز | پمپ‌کاران سرچاهی</t>
+          <t>کارگران ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | دکل‌بانان نفت و گاز | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کارگران کمکی استخراج معدن | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | ملوانان و روغن‌کاران شناورهای دریایی | اپراتورهای واحدهای خدمات چاه نفت و گاز | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | زمان واکنش | ادراک عمق | ثبات دست و بازو | دقت کنترل | هماهنگی چنداندامی | دید نزدیک | استدلال قیاسی | بیان شفاهی | درک شفاهی | چابکی دستی | توجه انتخابی | تشخیص گفتار | کنترل نرخ | دید دور | حساسیت شنوایی | وضوح گفتار | تجسم فضایی | استدلال استقرایی | سرعت ادراک | مرتب‌سازی اطلاعات | تعادل کلی بدن | انعطاف‌پذیری دامنه‌ای | چابکی انگشتان | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | جهت‌یابی پاسخ</t>
+          <t>حساسیت به مسئله | زمان عکس‌العمل | درک عمق | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | بینایی نزدیک | استدلال قیاسی | بیان شفاهی | درک شفاهی | مهارت دستی | توجه انتخابی | تشخیص گفتار | کنترل نرخ | بینایی دور | حساسیت شنوایی | وضوح گفتار | تجسم | استدلال استقرایی | سرعت ادراکی | ترتیب‌دهی اطلاعات | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | مهارت انگشتان | انعطاف‌پذیری دسته‌بندی | توجه شنیداری | جهت‌گیری پاسخ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | نصابان و تعمیرکاران خطوط انتقال نیرو | اپراتورهای درگ‌لاین و ماشین‌آلات حفاری و بارگیری در معادن روباز | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه تراش و تراشکاری فلز و پلاستیک | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک‌های ماشین‌آلات سنگین متحرک (به‌جز موتور) | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات ابزار چندکاره فلز و پلاستیک | اپراتورهای ماشین‌آلات مهندسی و تجهیزات ساختمانی | اپراتورهای دستگاه‌های شمع‌کوبی | ریگرها و سیم‌بکسل‌اندازان صنعتی | کارگران همه‌کاره دکل‌های نفت و گاز (راستابات) | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | اپراتورهای دستگاه شمع‌کوب | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | کارگران عمومی سکو و میادین نفت و گاز | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چنداندامی | دید دور | جهت‌یابی پاسخ | چابکی دستی | کنترل نرخ | زمان واکنش | ادراک عمق | حساسیت به مسئله | توجه شنیداری | دید نزدیک | قدرت تنه | استحکام ایستا | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | جهت‌یابی فضایی | سرعت ادراک | مرتب‌سازی اطلاعات | استدلال قیاسی | چابکی انگشتان | بیان شفاهی | درک شفاهی | دید پیرامونی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | بینایی دور | جهت‌گیری پاسخ | مهارت دستی | کنترل نرخ | زمان عکس‌العمل | درک عمق | حساسیت به مسئله | توجه شنیداری | بینایی نزدیک | قدرت تنه | قدرت ایستا | ثبات دست و بازو | توجه انتخابی | تجسم | جهت‌گیری فضایی | سرعت ادراکی | ترتیب‌دهی اطلاعات | استدلال قیاسی | مهارت انگشتان | بیان شفاهی | درک شفاهی | بینایی محیطی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>اپراتورهای ماشین‌آلات کشاورزی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | اپراتورهای ماشین‌آلات استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | اپراتورهای درگ‌لاین و ماشین‌آلات حفاری و بارگیری در معادن روباز | رانندگان تریلر و کامیون‌های سنگین | کارگران کمکی خطوط تولید | اپراتورهای بالابر و وینچ | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌آلات بارگیری و انتقال در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | مکانیک‌های ماشین‌آلات سنگین متحرک (به‌جز موتور) | اپراتورهای ماشین‌آلات مهندسی و تجهیزات ساختمانی | مکانیک‌های موتورهای کوچک و تجهیزات باغبانی | اپراتورهای ماشین‌آلات آسفالت‌کاری، تسطیح و تراکم‌سازی | اپراتورهای دستگاه‌های شمع‌کوبی | ریگرها و سیم‌بکسل‌اندازان صنعتی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای ماشین‌های استخراج پیوسته | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | مونتاژکاران موتور و سایر ماشین‌آلات | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | رانندگان خودروهای سنگین و کشنده‌ها | کمک‌کارگران خطوط تولید | اپراتورهای بالابر و وینچ | کارگران جابه‌جایی دستی بار، کالا و مصالح | اپراتورهای ماشین‌های بارگیری و حمل در معادن زیرزمینی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | اپراتورهای دستگاه شمع‌کوب | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ترابری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | انعطاف‌پذیری دامنه‌ای | هماهنگی چنداندامی | حساسیت به مسئله | استقامت | قدرت تنه | دقت کنترل | چابکی انگشتان</t>
+          <t>بینایی نزدیک | مهارت دستی | انعطاف‌پذیری دامنه حرکت | هماهنگی چند عضو | حساسیت به مسئله | استقامت | قدرت تنه | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان تجهیزات شست‌وشو، اسیدشویی و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات رنگ‌پاشی و پوشش‌دهی | نصابان و تعمیرکاران شیرآلات و سیستم‌های کنترلی صنعتی | ظرف‌شویان صنعتی | تعمیرکاران الکتروموتورها و ابزارهای برقی | اپراتورها و متصدیان کوره، دیگ پخت، اتوکلاو و خشک‌کن صنعتی | کارگران پرداخت و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنباده‌زنی، لپینگ و پرداخت فلز و پلاستیک | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | متصدیان خدمات و پاکبانان ساختمان (به‌جز خدمتکاران) | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشک‌شویی و لاندری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه فلزات | اپراتورهای پمپ (به‌جز پمپ‌های سرچاهی) | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون و تقطیر | سرویس‌کاران سپتیک‌تانک و لایروبان مجاری فاضلاب | سنگ‌زن‌ها، سنباده‌کاران و تیزکنندگان ابزار</t>
+          <t>اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | ظرف‌شویان | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | سرایداران و نظافتچیان، به‌جز خدمتکاران و نظافتچیان منازل | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان کوره‌های تصفیه و ذوب فلزات | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | ترابری | تولید و فرآوری | ریاضیات</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | حمل و نقل | تولید و فرآوری | ریاضیات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استحکام ایستا | قدرت تنه | هماهنگی چنداندامی | دید نزدیک | انعطاف‌پذیری دامنه‌ای | استقامت | چابکی دستی | درک شفاهی | ثبات دست و بازو | توجه انتخابی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | دید دور | نیروی دینامیکی | دقت کنترل</t>
+          <t>قدرت ایستا | قدرت تنه | هماهنگی چند عضو | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | استقامت | مهارت دستی | درک شفاهی | ثبات دست و بازو | توجه انتخابی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | بینایی دور | قدرت پویا | دقت کنترل</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های سنگ‌شکن، خردکن و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | کارگران کمکی استخراج معدن و نفت | کارگران کمکی خطوط تولید | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران خشک‌شویی و لاندری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | کارگران بازیافت و تفکیک پسماند | متصدیان انبار، ثبت ورود/خروج و کنترل موجودی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | متصدیان توزین، متراژ، کنترل و نمونه‌برداری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | کارگران ساختمانی | اپراتورها و متصدیان نوار نقاله | اپراتورهای جرثقیل و تاورکرین | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | کارگران کمکی استخراج معدن | کمک‌کارگران خطوط تولید | اپراتورهای بالابر و وینچ | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | کارگران بازیافت و تفکیک پسماند | کارمندان انبار، ارسال و دریافت کالا | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار برنامه‌ریزی شیفت و زمان‌بندی کار</t>
+          <t>Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | نرم‌افزار زمان‌بندی کار</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت</t>
+          <t>گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مکانیک | مدیریت و امور اداری | ایمنی و امنیت عمومی | آموزش و یادگیری | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و منابع انسانی</t>
+          <t>تولید و فرآوری | مکانیک | مدیریت و اداره | ایمنی و امنیت عمومی | آموزش و پرورش | خدمات مشتری و شخصی | زبان انگلیسی | پرسنل و منابع انسانی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت کنترل | دید نزدیک | هماهنگی چنداندامی | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | چابکی انگشتان | قدرت تنه | زمان واکنش | کنترل نرخ | توجه انتخابی | سرعت ادراک | انعطاف‌پذیری بستار | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | ادراک عمق | دید دور | سرعت حرکات اندام‌ها</t>
+          <t>مهارت دستی | دقت کنترل | بینایی نزدیک | هماهنگی چند عضو | ثبات دست و بازو | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | قدرت تنه | زمان عکس‌العمل | کنترل نرخ | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | درک عمق | بینایی دور | سرعت حرکت اعضا</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورهای کارخانه و سیستم‌های تصفیه مواد شیمیایی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، اسیدشویی و چربی‌زدایی فلزات | اپراتورها و متصدیان نوار نقاله | کارگران جمع‌آوری و پاکسازی پسماندهای پرخطر | کارگران کمکی استخراج معدن و نفت | کارگران کمکی خطوط تولید | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشک‌شویی و لاندری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیر و نگهداری تاسیسات | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | هماهنگ‌کنندگان و کارشناسان برنامه‌ریزی بازیافت | ماموران جمع‌آوری پسماند و مواد بازیافتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون و تقطیر | سرویس‌کاران سپتیک‌تانک و لایروبان مجاری فاضلاب | اپراتورهای تصفیه‌خانه و سیستم‌های آب و فاضلاب</t>
+          <t>اپراتورهای تأسیسات و سیستم‌های فرایندی صنایع شیمیایی | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورها و متصدیان تجهیزات شست‌وشو، نظافت و چربی‌زدایی فلزات | اپراتورها و متصدیان نوار نقاله | کارگران امحا و پاک‌سازی مواد خطرناک | کارگران کمکی استخراج معدن | کمک‌کارگران خطوط تولید | مکانیک‌های ماشین‌آلات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | هماهنگ‌کنندگان امور بازیافت | متصدیان و رانندگان جمع‌آوری پسماند و مواد بازیافتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دقت کنترل | کنترل نرخ | زمان واکنش | دید نزدیک | بیان شفاهی | حساسیت به مسئله | درک شفاهی | استحکام ایستا | چابکی دستی | مرتب‌سازی اطلاعات</t>
+          <t>ثبات دست و بازو | دقت کنترل | کنترل نرخ | زمان عکس‌العمل | بینایی نزدیک | بیان شفاهی | حساسیت به مسئله | درک شفاهی | قدرت ایستا | مهارت دستی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های سنگ‌شکن، خردکن و پرداخت | برشکاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | اپراتورها و متصدیان کوره، دیگ پخت، اتوکلاو و خشک‌کن صنعتی | کارگران پرداخت و سنباده‌زنی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنباده‌زنی، لپینگ و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه فرزکاری و رنده‌کاری فلز و پلاستیک | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش منسوجات | سنگ‌زن‌ها، سنباده‌کاران و تیزکنندگان ابزار | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان و اپراتورهای ماشین‌های برش، پانچ و پرس فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورها و متصدیان کوره‌ها، خشک‌کن‌ها و پاتیل‌های صنعتی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | کارگران بسته‌بندی دستی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان و اپراتورهای ماشین‌های نورد فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | خدمات مشتریان و خدمات فردی</t>
+          <t>تولید و فرآوری | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | قدرت تنه | حساسیت به مسئله | تشخیص گفتار | استحکام ایستا | هماهنگی چنداندامی | چابکی دستی | درک شفاهی</t>
+          <t>بینایی نزدیک | قدرت تنه | حساسیت به مسئله | تشخیص گفتار | قدرت ایستا | هماهنگی چند عضو | مهارت دستی | درک شفاهی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه چسب‌زنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های سنگ‌شکن، خردکن و پرداخت | برشکاران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات برش و اسلایس | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | اپراتورها و متصدیان دستگاه‌های برشته‌کاری، پخت و خشک‌کردن مواد غذایی و توتون | درجه‌بندان و تفکیک‌کنندگان محصولات کشاورزی | کارگران پرداخت و سنباده‌زنی دستی | کارگران کمکی خطوط تولید | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشک‌شویی و لاندری | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و همزن | قالب‌ریزان، شکل‌دهندگان و ریخته‌گران (به‌جز فلز و پلاستیک) | اپراتورها و متصدیان ماشین‌آلات بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون و تقطیر | خیاطان صنعتی و چرخکاران | متصدیان توزین، متراژ، کنترل و نمونه‌برداری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب (به‌جز اره‌کشی)</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات خردایش، آسیاب و پرداخت | برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | اپراتورهای ماشین‌آلات برشته‌کاری، پخت و خشک‌کن مواد غذایی و توتون | کارگران درجه‌بندی و تفکیک محصولات کشاورزی | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | کمک‌کارگران خطوط تولید | کارگران جابه‌جایی دستی بار، کالا و مصالح | کارگران خشکشویی و رختشویخانه | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های مخلوط‌کن و ترکیب مواد | شکل‌دهندگان و قالب‌ریزان غیرفلزی و غیرپلاستیکی | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات جداسازی، فیلتراسیون، شفاف‌سازی، ترسیب و تقطیر | چرخکاران صنعتی | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
